--- a/Motor_Driver_Board/Build/POS.xlsx
+++ b/Motor_Driver_Board/Build/POS.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Waseda\Motor_Driver_Board\Motor_Driver_Board\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C22DC71F-0394-4D02-BE00-5B6A0288BDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC8B2E3F-E172-4569-89A6-978255865AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="1740" windowWidth="19200" windowHeight="11170" xr2:uid="{9C82B0BE-14C0-4ADC-A129-67AF8C25F390}"/>
+    <workbookView xWindow="1740" yWindow="1740" windowWidth="19200" windowHeight="11170" xr2:uid="{D96079CC-0560-4A60-A644-F47ABBB7F4D2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Motor_Driver_Board-all-pos" sheetId="1" r:id="rId1"/>
+    <sheet name="POS" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -965,7 +965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66A74BD-C2FF-454B-9285-EFCAB5254B8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03960F8-EEC7-4AC9-B1DB-346459129DBB}">
   <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
